--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120016455</v>
+        <v>120016451</v>
       </c>
       <c r="B10" t="n">
-        <v>78262</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505301</v>
+        <v>505439</v>
       </c>
       <c r="R10" t="n">
-        <v>7133536</v>
+        <v>7133195</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,6 +1644,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016451</v>
+        <v>120016455</v>
       </c>
       <c r="B11" t="n">
-        <v>57463</v>
+        <v>78262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505439</v>
+        <v>505301</v>
       </c>
       <c r="R11" t="n">
-        <v>7133195</v>
+        <v>7133536</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1746,11 +1751,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016449</v>
+        <v>120016454</v>
       </c>
       <c r="B20" t="n">
-        <v>89633</v>
+        <v>90839</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>6008693</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505475</v>
+        <v>505318</v>
       </c>
       <c r="R20" t="n">
-        <v>7133313</v>
+        <v>7133504</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2674,6 +2674,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,10 +2705,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016645</v>
+        <v>120016449</v>
       </c>
       <c r="B21" t="n">
-        <v>79115</v>
+        <v>89633</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,37 +2721,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505457</v>
+        <v>505475</v>
       </c>
       <c r="R21" t="n">
-        <v>7133307</v>
+        <v>7133313</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2787,7 +2789,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2806,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016454</v>
+        <v>120016645</v>
       </c>
       <c r="B22" t="n">
-        <v>90839</v>
+        <v>79115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2818,38 +2819,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6008693</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505318</v>
+        <v>505457</v>
       </c>
       <c r="R22" t="n">
-        <v>7133504</v>
+        <v>7133307</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2884,17 +2888,13 @@
           <t>2024-09-25</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016619</v>
+        <v>119987715</v>
       </c>
       <c r="B23" t="n">
         <v>92030</v>
@@ -2947,22 +2947,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505447</v>
+        <v>505497</v>
       </c>
       <c r="R23" t="n">
-        <v>7133184</v>
+        <v>7133163</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3000,7 +2997,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3019,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119987715</v>
+        <v>120016619</v>
       </c>
       <c r="B24" t="n">
         <v>92030</v>
@@ -3053,19 +3049,22 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505497</v>
+        <v>505447</v>
       </c>
       <c r="R24" t="n">
-        <v>7133163</v>
+        <v>7133184</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3103,6 +3102,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119996930</v>
+        <v>119987715</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>92030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505471</v>
+        <v>505497</v>
       </c>
       <c r="R8" t="n">
-        <v>7133319</v>
+        <v>7133163</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120016462</v>
+        <v>119996930</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,41 +1478,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505473</v>
+        <v>505471</v>
       </c>
       <c r="R9" t="n">
-        <v>7133190</v>
+        <v>7133319</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120016451</v>
+        <v>119985349</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,37 +1584,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505439</v>
+        <v>505524</v>
       </c>
       <c r="R10" t="n">
-        <v>7133195</v>
+        <v>7133131</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,11 +1644,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016455</v>
+        <v>120016460</v>
       </c>
       <c r="B11" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,21 +1686,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505301</v>
+        <v>505439</v>
       </c>
       <c r="R11" t="n">
-        <v>7133536</v>
+        <v>7133195</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,10 +1772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120016460</v>
+        <v>119987738</v>
       </c>
       <c r="B12" t="n">
-        <v>78171</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,34 +1788,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505439</v>
+        <v>505487</v>
       </c>
       <c r="R12" t="n">
-        <v>7133195</v>
+        <v>7133194</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120016450</v>
+        <v>120016449</v>
       </c>
       <c r="B13" t="n">
         <v>89633</v>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505490</v>
+        <v>505475</v>
       </c>
       <c r="R13" t="n">
-        <v>7133227</v>
+        <v>7133313</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120016461</v>
+        <v>120016453</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,25 +1993,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505294</v>
+        <v>505463</v>
       </c>
       <c r="R14" t="n">
-        <v>7133539</v>
+        <v>7133176</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119985349</v>
+        <v>120016462</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,41 +2197,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505524</v>
+        <v>505473</v>
       </c>
       <c r="R16" t="n">
-        <v>7133131</v>
+        <v>7133190</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120016456</v>
+        <v>119999926</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,37 +2303,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505473</v>
+        <v>505346</v>
       </c>
       <c r="R17" t="n">
-        <v>7133215</v>
+        <v>7133517</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119999926</v>
+        <v>120016455</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,37 +2405,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505346</v>
+        <v>505301</v>
       </c>
       <c r="R18" t="n">
-        <v>7133517</v>
+        <v>7133536</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119987738</v>
+        <v>120016450</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
+        <v>89633</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,39 +2507,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505487</v>
+        <v>505490</v>
       </c>
       <c r="R19" t="n">
-        <v>7133194</v>
+        <v>7133227</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2598,10 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016454</v>
+        <v>120016461</v>
       </c>
       <c r="B20" t="n">
-        <v>90839</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2605,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6008693</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505318</v>
+        <v>505294</v>
       </c>
       <c r="R20" t="n">
-        <v>7133504</v>
+        <v>7133539</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2674,11 +2669,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,10 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016449</v>
+        <v>120016451</v>
       </c>
       <c r="B21" t="n">
-        <v>89633</v>
+        <v>57463</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,21 +2711,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2745,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505475</v>
+        <v>505439</v>
       </c>
       <c r="R21" t="n">
-        <v>7133313</v>
+        <v>7133195</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2781,6 +2771,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,10 +2908,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119987715</v>
+        <v>120016454</v>
       </c>
       <c r="B23" t="n">
-        <v>92030</v>
+        <v>90839</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,41 +2920,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>6008693</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505497</v>
+        <v>505318</v>
       </c>
       <c r="R23" t="n">
-        <v>7133163</v>
+        <v>7133504</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2989,6 +2984,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3015,10 +3015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016619</v>
+        <v>120016456</v>
       </c>
       <c r="B24" t="n">
-        <v>92030</v>
+        <v>78262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3031,37 +3031,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505447</v>
+        <v>505473</v>
       </c>
       <c r="R24" t="n">
-        <v>7133184</v>
+        <v>7133215</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3102,7 +3099,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3121,10 +3117,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016458</v>
+        <v>120016619</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>92030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,34 +3133,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505303</v>
+        <v>505447</v>
       </c>
       <c r="R25" t="n">
-        <v>7133532</v>
+        <v>7133184</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3205,6 +3204,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120016453</v>
+        <v>120016458</v>
       </c>
       <c r="B26" t="n">
-        <v>92030</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505463</v>
+        <v>505303</v>
       </c>
       <c r="R26" t="n">
-        <v>7133176</v>
+        <v>7133532</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3434,117 +3434,6 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>119986968</v>
-      </c>
-      <c r="B28" t="n">
-        <v>91886</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>232140</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tajgataggsvamp</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Phellodon secretus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>505489</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7133136</v>
-      </c>
-      <c r="S28" t="n">
-        <v>15</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119996930</v>
+        <v>119985349</v>
       </c>
       <c r="B9" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505471</v>
+        <v>505524</v>
       </c>
       <c r="R9" t="n">
-        <v>7133319</v>
+        <v>7133131</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119985349</v>
+        <v>119996930</v>
       </c>
       <c r="B10" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,13 +1608,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505524</v>
+        <v>505471</v>
       </c>
       <c r="R10" t="n">
-        <v>7133131</v>
+        <v>7133319</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119987715</v>
+        <v>120016453</v>
       </c>
       <c r="B8" t="n">
         <v>92030</v>
@@ -1400,17 +1400,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505497</v>
+        <v>505463</v>
       </c>
       <c r="R8" t="n">
-        <v>7133163</v>
+        <v>7133176</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119985349</v>
+        <v>119987715</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>92030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505524</v>
+        <v>505497</v>
       </c>
       <c r="R9" t="n">
-        <v>7133131</v>
+        <v>7133163</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119996930</v>
+        <v>120016454</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>90839</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,41 +1580,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6008693</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505471</v>
+        <v>505318</v>
       </c>
       <c r="R10" t="n">
-        <v>7133319</v>
+        <v>7133504</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,6 +1644,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119987738</v>
+        <v>120016619</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>92030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,39 +1793,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505487</v>
+        <v>505447</v>
       </c>
       <c r="R12" t="n">
-        <v>7133194</v>
+        <v>7133184</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1861,6 +1864,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1981,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120016453</v>
+        <v>119999926</v>
       </c>
       <c r="B14" t="n">
-        <v>92030</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,37 +2001,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505463</v>
+        <v>505346</v>
       </c>
       <c r="R14" t="n">
-        <v>7133176</v>
+        <v>7133517</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120016459</v>
+        <v>119996930</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,37 +2103,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505434</v>
+        <v>505471</v>
       </c>
       <c r="R15" t="n">
-        <v>7133465</v>
+        <v>7133319</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2185,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120016462</v>
+        <v>120016455</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,25 +2201,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2225,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505473</v>
+        <v>505301</v>
       </c>
       <c r="R16" t="n">
-        <v>7133190</v>
+        <v>7133536</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2287,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119999926</v>
+        <v>120016459</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2323,17 +2327,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505346</v>
+        <v>505434</v>
       </c>
       <c r="R17" t="n">
-        <v>7133517</v>
+        <v>7133465</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2389,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016455</v>
+        <v>120016461</v>
       </c>
       <c r="B18" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2401,25 +2405,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505301</v>
+        <v>505294</v>
       </c>
       <c r="R18" t="n">
-        <v>7133536</v>
+        <v>7133539</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2491,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120016450</v>
+        <v>119987738</v>
       </c>
       <c r="B19" t="n">
-        <v>89633</v>
+        <v>57463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,34 +2511,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505490</v>
+        <v>505487</v>
       </c>
       <c r="R19" t="n">
-        <v>7133227</v>
+        <v>7133194</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2593,10 +2602,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016461</v>
+        <v>119985349</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,41 +2614,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505294</v>
+        <v>505524</v>
       </c>
       <c r="R20" t="n">
-        <v>7133539</v>
+        <v>7133131</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2695,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016451</v>
+        <v>120016450</v>
       </c>
       <c r="B21" t="n">
-        <v>57463</v>
+        <v>89633</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,21 +2720,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2735,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505439</v>
+        <v>505490</v>
       </c>
       <c r="R21" t="n">
-        <v>7133195</v>
+        <v>7133227</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2771,11 +2780,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,10 +2806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016645</v>
+        <v>120016451</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>57463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2818,37 +2822,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505457</v>
+        <v>505439</v>
       </c>
       <c r="R22" t="n">
-        <v>7133307</v>
+        <v>7133195</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2883,13 +2884,17 @@
           <t>2024-09-25</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2908,10 +2913,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016454</v>
+        <v>120016645</v>
       </c>
       <c r="B23" t="n">
-        <v>90839</v>
+        <v>79115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2920,38 +2925,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6008693</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505318</v>
+        <v>505457</v>
       </c>
       <c r="R23" t="n">
-        <v>7133504</v>
+        <v>7133307</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2986,17 +2994,13 @@
           <t>2024-09-25</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3015,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016456</v>
+        <v>120016458</v>
       </c>
       <c r="B24" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3031,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3055,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505473</v>
+        <v>505303</v>
       </c>
       <c r="R24" t="n">
-        <v>7133215</v>
+        <v>7133532</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3117,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016619</v>
+        <v>120016456</v>
       </c>
       <c r="B25" t="n">
-        <v>92030</v>
+        <v>78262</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3133,37 +3137,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505447</v>
+        <v>505473</v>
       </c>
       <c r="R25" t="n">
-        <v>7133184</v>
+        <v>7133215</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3204,7 +3205,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120016458</v>
+        <v>120016462</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,25 +3235,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505303</v>
+        <v>505473</v>
       </c>
       <c r="R26" t="n">
-        <v>7133532</v>
+        <v>7133190</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -2393,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016461</v>
+        <v>119987738</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,38 +2405,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505294</v>
+        <v>505487</v>
       </c>
       <c r="R18" t="n">
-        <v>7133539</v>
+        <v>7133194</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2495,10 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119987738</v>
+        <v>120016461</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,43 +2512,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505487</v>
+        <v>505294</v>
       </c>
       <c r="R19" t="n">
-        <v>7133194</v>
+        <v>7133539</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120016453</v>
+        <v>120016645</v>
       </c>
       <c r="B8" t="n">
-        <v>92030</v>
+        <v>79115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,34 +1380,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505463</v>
+        <v>505457</v>
       </c>
       <c r="R8" t="n">
-        <v>7133176</v>
+        <v>7133307</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1448,6 +1451,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1466,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119987715</v>
+        <v>119985349</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505497</v>
+        <v>505524</v>
       </c>
       <c r="R9" t="n">
-        <v>7133163</v>
+        <v>7133131</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1675,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016460</v>
+        <v>120016462</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,25 +1691,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505439</v>
+        <v>505473</v>
       </c>
       <c r="R11" t="n">
-        <v>7133195</v>
+        <v>7133190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120016619</v>
+        <v>119987738</v>
       </c>
       <c r="B12" t="n">
-        <v>92030</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,37 +1797,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505447</v>
+        <v>505487</v>
       </c>
       <c r="R12" t="n">
-        <v>7133184</v>
+        <v>7133194</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,7 +1870,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,10 +1888,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120016449</v>
+        <v>119996930</v>
       </c>
       <c r="B13" t="n">
-        <v>89633</v>
+        <v>78263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,37 +1904,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505475</v>
+        <v>505471</v>
       </c>
       <c r="R13" t="n">
-        <v>7133313</v>
+        <v>7133319</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119999926</v>
+        <v>120016453</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>92030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,37 +2006,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505346</v>
+        <v>505463</v>
       </c>
       <c r="R14" t="n">
-        <v>7133517</v>
+        <v>7133176</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119996930</v>
+        <v>119999926</v>
       </c>
       <c r="B15" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,21 +2108,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,13 +2132,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505471</v>
+        <v>505346</v>
       </c>
       <c r="R15" t="n">
-        <v>7133319</v>
+        <v>7133517</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2291,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120016459</v>
+        <v>120016456</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,21 +2312,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2331,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505434</v>
+        <v>505473</v>
       </c>
       <c r="R17" t="n">
-        <v>7133465</v>
+        <v>7133215</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2393,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119987738</v>
+        <v>120016450</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>89633</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,39 +2414,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505487</v>
+        <v>505490</v>
       </c>
       <c r="R18" t="n">
-        <v>7133194</v>
+        <v>7133227</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120016461</v>
+        <v>120016459</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2512,25 +2512,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505294</v>
+        <v>505434</v>
       </c>
       <c r="R19" t="n">
-        <v>7133539</v>
+        <v>7133465</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2602,10 +2602,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119985349</v>
+        <v>120016619</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
+        <v>92030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2618,37 +2618,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505524</v>
+        <v>505447</v>
       </c>
       <c r="R20" t="n">
-        <v>7133131</v>
+        <v>7133184</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,6 +2689,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2704,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016450</v>
+        <v>120016451</v>
       </c>
       <c r="B21" t="n">
-        <v>89633</v>
+        <v>57463</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2720,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2744,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505490</v>
+        <v>505439</v>
       </c>
       <c r="R21" t="n">
-        <v>7133227</v>
+        <v>7133195</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2780,6 +2784,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2806,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016451</v>
+        <v>120016460</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>78171</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2882,11 +2891,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2913,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016645</v>
+        <v>120016449</v>
       </c>
       <c r="B23" t="n">
-        <v>79115</v>
+        <v>89633</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2929,37 +2933,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505457</v>
+        <v>505475</v>
       </c>
       <c r="R23" t="n">
-        <v>7133307</v>
+        <v>7133313</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3000,7 +3001,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016458</v>
+        <v>119987715</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>92030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,37 +3035,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505303</v>
+        <v>505497</v>
       </c>
       <c r="R24" t="n">
-        <v>7133532</v>
+        <v>7133163</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016456</v>
+        <v>120016461</v>
       </c>
       <c r="B25" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3133,25 +3133,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505473</v>
+        <v>505294</v>
       </c>
       <c r="R25" t="n">
-        <v>7133215</v>
+        <v>7133539</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120016462</v>
+        <v>120016458</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,25 +3235,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505473</v>
+        <v>505303</v>
       </c>
       <c r="R26" t="n">
-        <v>7133190</v>
+        <v>7133532</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -2917,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016449</v>
+        <v>119987715</v>
       </c>
       <c r="B23" t="n">
-        <v>89633</v>
+        <v>92030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505475</v>
+        <v>505497</v>
       </c>
       <c r="R23" t="n">
-        <v>7133313</v>
+        <v>7133163</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119987715</v>
+        <v>120016449</v>
       </c>
       <c r="B24" t="n">
-        <v>92030</v>
+        <v>89633</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,37 +3035,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505497</v>
+        <v>505475</v>
       </c>
       <c r="R24" t="n">
-        <v>7133163</v>
+        <v>7133313</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -2917,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119987715</v>
+        <v>120016449</v>
       </c>
       <c r="B23" t="n">
-        <v>92030</v>
+        <v>89633</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505497</v>
+        <v>505475</v>
       </c>
       <c r="R23" t="n">
-        <v>7133163</v>
+        <v>7133313</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016449</v>
+        <v>119987715</v>
       </c>
       <c r="B24" t="n">
-        <v>89633</v>
+        <v>92030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,37 +3035,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505475</v>
+        <v>505497</v>
       </c>
       <c r="R24" t="n">
-        <v>7133313</v>
+        <v>7133163</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>88774724</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120016645</v>
+        <v>120016449</v>
       </c>
       <c r="B8" t="n">
-        <v>79115</v>
+        <v>89650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,37 +1380,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505457</v>
+        <v>505475</v>
       </c>
       <c r="R8" t="n">
-        <v>7133307</v>
+        <v>7133313</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,7 +1448,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1470,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119985349</v>
+        <v>120016454</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>90857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,41 +1478,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6008693</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505524</v>
+        <v>505318</v>
       </c>
       <c r="R9" t="n">
-        <v>7133131</v>
+        <v>7133504</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,6 +1542,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120016454</v>
+        <v>119999926</v>
       </c>
       <c r="B10" t="n">
-        <v>90839</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,41 +1585,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6008693</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505318</v>
+        <v>505346</v>
       </c>
       <c r="R10" t="n">
-        <v>7133504</v>
+        <v>7133517</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,11 +1649,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016462</v>
+        <v>119987738</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,38 +1687,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505473</v>
+        <v>505487</v>
       </c>
       <c r="R11" t="n">
-        <v>7133190</v>
+        <v>7133194</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1781,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119987738</v>
+        <v>120016458</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,39 +1798,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505487</v>
+        <v>505303</v>
       </c>
       <c r="R12" t="n">
-        <v>7133194</v>
+        <v>7133532</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1888,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119996930</v>
+        <v>120016450</v>
       </c>
       <c r="B13" t="n">
-        <v>78263</v>
+        <v>89650</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,37 +1900,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505471</v>
+        <v>505490</v>
       </c>
       <c r="R13" t="n">
-        <v>7133319</v>
+        <v>7133227</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,10 +1986,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120016453</v>
+        <v>120016455</v>
       </c>
       <c r="B14" t="n">
-        <v>92030</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,21 +2002,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2030,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505463</v>
+        <v>505301</v>
       </c>
       <c r="R14" t="n">
-        <v>7133176</v>
+        <v>7133536</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2092,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119999926</v>
+        <v>119996930</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>78279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,21 +2104,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2132,13 +2128,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505346</v>
+        <v>505471</v>
       </c>
       <c r="R15" t="n">
-        <v>7133517</v>
+        <v>7133319</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,10 +2190,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120016455</v>
+        <v>120016645</v>
       </c>
       <c r="B16" t="n">
-        <v>78262</v>
+        <v>79131</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,34 +2206,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505301</v>
+        <v>505457</v>
       </c>
       <c r="R16" t="n">
-        <v>7133536</v>
+        <v>7133307</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2278,6 +2277,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120016456</v>
+        <v>119985349</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,37 +2312,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505473</v>
+        <v>505524</v>
       </c>
       <c r="R17" t="n">
-        <v>7133215</v>
+        <v>7133131</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016450</v>
+        <v>120016451</v>
       </c>
       <c r="B18" t="n">
-        <v>89633</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,21 +2414,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505490</v>
+        <v>505439</v>
       </c>
       <c r="R18" t="n">
-        <v>7133227</v>
+        <v>7133195</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2474,6 +2474,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2500,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120016459</v>
+        <v>119987715</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>92048</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,37 +2521,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505434</v>
+        <v>505497</v>
       </c>
       <c r="R19" t="n">
-        <v>7133465</v>
+        <v>7133163</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2605,7 +2610,7 @@
         <v>120016619</v>
       </c>
       <c r="B20" t="n">
-        <v>92030</v>
+        <v>92048</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2708,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016451</v>
+        <v>120016461</v>
       </c>
       <c r="B21" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2720,25 +2725,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505439</v>
+        <v>505294</v>
       </c>
       <c r="R21" t="n">
-        <v>7133195</v>
+        <v>7133539</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2784,11 +2789,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016460</v>
+        <v>120016459</v>
       </c>
       <c r="B22" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505439</v>
+        <v>505434</v>
       </c>
       <c r="R22" t="n">
-        <v>7133195</v>
+        <v>7133465</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016449</v>
+        <v>120016453</v>
       </c>
       <c r="B23" t="n">
-        <v>89633</v>
+        <v>92048</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505475</v>
+        <v>505463</v>
       </c>
       <c r="R23" t="n">
-        <v>7133313</v>
+        <v>7133176</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119987715</v>
+        <v>120016456</v>
       </c>
       <c r="B24" t="n">
-        <v>92030</v>
+        <v>78278</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,37 +3035,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505497</v>
+        <v>505473</v>
       </c>
       <c r="R24" t="n">
-        <v>7133163</v>
+        <v>7133215</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016461</v>
+        <v>120016460</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>78187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3133,25 +3133,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505294</v>
+        <v>505439</v>
       </c>
       <c r="R25" t="n">
-        <v>7133539</v>
+        <v>7133195</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120016458</v>
+        <v>120016462</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,25 +3235,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505303</v>
+        <v>505473</v>
       </c>
       <c r="R26" t="n">
-        <v>7133532</v>
+        <v>7133190</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3328,7 +3328,7 @@
         <v>120016452</v>
       </c>
       <c r="B27" t="n">
-        <v>91886</v>
+        <v>91904</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016459</v>
+        <v>120016453</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505434</v>
+        <v>505463</v>
       </c>
       <c r="R22" t="n">
-        <v>7133465</v>
+        <v>7133176</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016453</v>
+        <v>120016459</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505463</v>
+        <v>505434</v>
       </c>
       <c r="R23" t="n">
-        <v>7133176</v>
+        <v>7133465</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016456</v>
+        <v>120016460</v>
       </c>
       <c r="B24" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505473</v>
+        <v>505439</v>
       </c>
       <c r="R24" t="n">
-        <v>7133215</v>
+        <v>7133195</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016460</v>
+        <v>120016456</v>
       </c>
       <c r="B25" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505439</v>
+        <v>505473</v>
       </c>
       <c r="R25" t="n">
-        <v>7133195</v>
+        <v>7133215</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120016449</v>
+        <v>120016450</v>
       </c>
       <c r="B8" t="n">
         <v>89650</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505475</v>
+        <v>505490</v>
       </c>
       <c r="R8" t="n">
-        <v>7133313</v>
+        <v>7133227</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120016454</v>
+        <v>119985349</v>
       </c>
       <c r="B9" t="n">
-        <v>90857</v>
+        <v>78187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,41 +1478,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6008693</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505318</v>
+        <v>505524</v>
       </c>
       <c r="R9" t="n">
-        <v>7133504</v>
+        <v>7133131</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,11 +1542,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119999926</v>
+        <v>120016449</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,37 +1584,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505346</v>
+        <v>505475</v>
       </c>
       <c r="R10" t="n">
-        <v>7133517</v>
+        <v>7133313</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,7 +1670,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119987738</v>
+        <v>120016451</v>
       </c>
       <c r="B11" t="n">
         <v>57473</v>
@@ -1709,21 +1704,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505487</v>
+        <v>505439</v>
       </c>
       <c r="R11" t="n">
-        <v>7133194</v>
+        <v>7133195</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1756,6 +1746,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120016458</v>
+        <v>120016619</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,34 +1793,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505303</v>
+        <v>505447</v>
       </c>
       <c r="R12" t="n">
-        <v>7133532</v>
+        <v>7133184</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1866,6 +1864,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1884,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120016450</v>
+        <v>120016459</v>
       </c>
       <c r="B13" t="n">
-        <v>89650</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,21 +1899,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1924,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505490</v>
+        <v>505434</v>
       </c>
       <c r="R13" t="n">
-        <v>7133227</v>
+        <v>7133465</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1986,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120016455</v>
+        <v>120016454</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>90857</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1998,25 +1997,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6008693</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2026,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505301</v>
+        <v>505318</v>
       </c>
       <c r="R14" t="n">
-        <v>7133536</v>
+        <v>7133504</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2062,6 +2061,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119996930</v>
+        <v>120016462</v>
       </c>
       <c r="B15" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,41 +2104,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505471</v>
+        <v>505473</v>
       </c>
       <c r="R15" t="n">
-        <v>7133319</v>
+        <v>7133190</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2190,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120016645</v>
+        <v>120016453</v>
       </c>
       <c r="B16" t="n">
-        <v>79131</v>
+        <v>92048</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,37 +2210,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505457</v>
+        <v>505463</v>
       </c>
       <c r="R16" t="n">
-        <v>7133307</v>
+        <v>7133176</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2277,7 +2278,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119985349</v>
+        <v>119999926</v>
       </c>
       <c r="B17" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505524</v>
+        <v>505346</v>
       </c>
       <c r="R17" t="n">
-        <v>7133131</v>
+        <v>7133517</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016451</v>
+        <v>119987738</v>
       </c>
       <c r="B18" t="n">
         <v>57473</v>
@@ -2432,16 +2432,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505439</v>
+        <v>505487</v>
       </c>
       <c r="R18" t="n">
-        <v>7133195</v>
+        <v>7133194</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2474,11 +2479,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119987715</v>
+        <v>119996930</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>78279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2521,21 +2521,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505497</v>
+        <v>505471</v>
       </c>
       <c r="R19" t="n">
-        <v>7133163</v>
+        <v>7133319</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016619</v>
+        <v>120016458</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,37 +2623,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505447</v>
+        <v>505303</v>
       </c>
       <c r="R20" t="n">
-        <v>7133184</v>
+        <v>7133532</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2691,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2713,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016461</v>
+        <v>120016455</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,25 +2721,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505294</v>
+        <v>505301</v>
       </c>
       <c r="R21" t="n">
-        <v>7133539</v>
+        <v>7133536</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2815,10 +2811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016453</v>
+        <v>120016460</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2827,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2851,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505463</v>
+        <v>505439</v>
       </c>
       <c r="R22" t="n">
-        <v>7133176</v>
+        <v>7133195</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2917,10 +2913,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016459</v>
+        <v>120016456</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2929,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505434</v>
+        <v>505473</v>
       </c>
       <c r="R23" t="n">
-        <v>7133465</v>
+        <v>7133215</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3019,10 +3015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016460</v>
+        <v>120016461</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3031,25 +3027,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3055,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505439</v>
+        <v>505294</v>
       </c>
       <c r="R24" t="n">
-        <v>7133195</v>
+        <v>7133539</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3121,10 +3117,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016456</v>
+        <v>120016645</v>
       </c>
       <c r="B25" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,34 +3133,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505473</v>
+        <v>505457</v>
       </c>
       <c r="R25" t="n">
-        <v>7133215</v>
+        <v>7133307</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3205,6 +3204,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120016462</v>
+        <v>119987715</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,41 +3235,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505473</v>
+        <v>505497</v>
       </c>
       <c r="R26" t="n">
-        <v>7133190</v>
+        <v>7133163</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119985349</v>
+        <v>120016449</v>
       </c>
       <c r="B9" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,37 +1482,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505524</v>
+        <v>505475</v>
       </c>
       <c r="R9" t="n">
-        <v>7133131</v>
+        <v>7133313</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120016449</v>
+        <v>119985349</v>
       </c>
       <c r="B10" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,37 +1584,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505475</v>
+        <v>505524</v>
       </c>
       <c r="R10" t="n">
-        <v>7133313</v>
+        <v>7133131</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120016450</v>
+        <v>120016456</v>
       </c>
       <c r="B8" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505490</v>
+        <v>505473</v>
       </c>
       <c r="R8" t="n">
-        <v>7133227</v>
+        <v>7133215</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120016449</v>
+        <v>120016451</v>
       </c>
       <c r="B9" t="n">
-        <v>89650</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505475</v>
+        <v>505439</v>
       </c>
       <c r="R9" t="n">
-        <v>7133313</v>
+        <v>7133195</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1542,6 +1542,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119985349</v>
+        <v>120016454</v>
       </c>
       <c r="B10" t="n">
-        <v>78187</v>
+        <v>90857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,41 +1585,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6008693</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505524</v>
+        <v>505318</v>
       </c>
       <c r="R10" t="n">
-        <v>7133131</v>
+        <v>7133504</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,6 +1649,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016451</v>
+        <v>120016619</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>92048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,34 +1696,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505439</v>
+        <v>505447</v>
       </c>
       <c r="R11" t="n">
-        <v>7133195</v>
+        <v>7133184</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1748,17 +1761,13 @@
           <t>2024-09-25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120016619</v>
+        <v>119996930</v>
       </c>
       <c r="B12" t="n">
-        <v>92048</v>
+        <v>78279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,40 +1802,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505447</v>
+        <v>505471</v>
       </c>
       <c r="R12" t="n">
-        <v>7133184</v>
+        <v>7133319</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1870,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,7 +1888,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120016459</v>
+        <v>120016458</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1923,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505434</v>
+        <v>505303</v>
       </c>
       <c r="R13" t="n">
-        <v>7133465</v>
+        <v>7133532</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1985,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120016454</v>
+        <v>119987738</v>
       </c>
       <c r="B14" t="n">
-        <v>90857</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,38 +2002,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6008693</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505318</v>
+        <v>505487</v>
       </c>
       <c r="R14" t="n">
-        <v>7133504</v>
+        <v>7133194</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2061,11 +2071,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120016462</v>
+        <v>120016459</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2104,25 +2109,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505473</v>
+        <v>505434</v>
       </c>
       <c r="R15" t="n">
-        <v>7133190</v>
+        <v>7133465</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2194,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120016453</v>
+        <v>120016455</v>
       </c>
       <c r="B16" t="n">
-        <v>92048</v>
+        <v>78278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,21 +2215,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2234,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505463</v>
+        <v>505301</v>
       </c>
       <c r="R16" t="n">
-        <v>7133176</v>
+        <v>7133536</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2296,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119999926</v>
+        <v>119987715</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,21 +2317,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2336,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505346</v>
+        <v>505497</v>
       </c>
       <c r="R17" t="n">
-        <v>7133517</v>
+        <v>7133163</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2398,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119987738</v>
+        <v>120016461</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2410,43 +2415,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505487</v>
+        <v>505294</v>
       </c>
       <c r="R18" t="n">
-        <v>7133194</v>
+        <v>7133539</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119996930</v>
+        <v>120016460</v>
       </c>
       <c r="B19" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2521,37 +2521,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505471</v>
+        <v>505439</v>
       </c>
       <c r="R19" t="n">
-        <v>7133319</v>
+        <v>7133195</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016458</v>
+        <v>120016453</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,21 +2623,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505303</v>
+        <v>505463</v>
       </c>
       <c r="R20" t="n">
-        <v>7133532</v>
+        <v>7133176</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016455</v>
+        <v>120016449</v>
       </c>
       <c r="B21" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,21 +2725,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505301</v>
+        <v>505475</v>
       </c>
       <c r="R21" t="n">
-        <v>7133536</v>
+        <v>7133313</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016460</v>
+        <v>119999926</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,37 +2827,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505439</v>
+        <v>505346</v>
       </c>
       <c r="R22" t="n">
-        <v>7133195</v>
+        <v>7133517</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016456</v>
+        <v>120016462</v>
       </c>
       <c r="B23" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,25 +2925,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
         <v>505473</v>
       </c>
       <c r="R23" t="n">
-        <v>7133215</v>
+        <v>7133190</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016461</v>
+        <v>120016645</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3027,38 +3027,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505294</v>
+        <v>505457</v>
       </c>
       <c r="R24" t="n">
-        <v>7133539</v>
+        <v>7133307</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3099,6 +3102,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3117,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016645</v>
+        <v>120016450</v>
       </c>
       <c r="B25" t="n">
-        <v>79131</v>
+        <v>89650</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3133,37 +3137,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505457</v>
+        <v>505490</v>
       </c>
       <c r="R25" t="n">
-        <v>7133307</v>
+        <v>7133227</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3204,7 +3205,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119987715</v>
+        <v>119985349</v>
       </c>
       <c r="B26" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505497</v>
+        <v>505524</v>
       </c>
       <c r="R26" t="n">
-        <v>7133163</v>
+        <v>7133131</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -2505,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120016460</v>
+        <v>120016453</v>
       </c>
       <c r="B19" t="n">
-        <v>78187</v>
+        <v>92048</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2521,21 +2521,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505439</v>
+        <v>505463</v>
       </c>
       <c r="R19" t="n">
-        <v>7133195</v>
+        <v>7133176</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016453</v>
+        <v>120016460</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,21 +2623,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505463</v>
+        <v>505439</v>
       </c>
       <c r="R20" t="n">
-        <v>7133176</v>
+        <v>7133195</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120016451</v>
+        <v>120016645</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>79131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,34 +1482,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505439</v>
+        <v>505457</v>
       </c>
       <c r="R9" t="n">
-        <v>7133195</v>
+        <v>7133307</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,17 +1547,13 @@
           <t>2024-09-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1573,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120016454</v>
+        <v>120016459</v>
       </c>
       <c r="B10" t="n">
-        <v>90857</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,25 +1584,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6008693</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505318</v>
+        <v>505434</v>
       </c>
       <c r="R10" t="n">
-        <v>7133504</v>
+        <v>7133465</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1649,11 +1648,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119996930</v>
+        <v>120016454</v>
       </c>
       <c r="B12" t="n">
-        <v>78279</v>
+        <v>90857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,41 +1792,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6008693</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505471</v>
+        <v>505318</v>
       </c>
       <c r="R12" t="n">
-        <v>7133319</v>
+        <v>7133504</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,6 +1856,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1888,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120016458</v>
+        <v>120016460</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1928,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505303</v>
+        <v>505439</v>
       </c>
       <c r="R13" t="n">
-        <v>7133532</v>
+        <v>7133195</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1990,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119987738</v>
+        <v>120016461</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,43 +2001,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505487</v>
+        <v>505294</v>
       </c>
       <c r="R14" t="n">
-        <v>7133194</v>
+        <v>7133539</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2097,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120016459</v>
+        <v>120016458</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2137,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505434</v>
+        <v>505303</v>
       </c>
       <c r="R15" t="n">
-        <v>7133465</v>
+        <v>7133532</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2199,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120016455</v>
+        <v>119996930</v>
       </c>
       <c r="B16" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,37 +2209,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505301</v>
+        <v>505471</v>
       </c>
       <c r="R16" t="n">
-        <v>7133536</v>
+        <v>7133319</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119987715</v>
+        <v>119987738</v>
       </c>
       <c r="B17" t="n">
-        <v>92048</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,37 +2311,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505497</v>
+        <v>505487</v>
       </c>
       <c r="R17" t="n">
-        <v>7133163</v>
+        <v>7133194</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2403,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016461</v>
+        <v>119985349</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,41 +2414,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505294</v>
+        <v>505524</v>
       </c>
       <c r="R18" t="n">
-        <v>7133539</v>
+        <v>7133131</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016460</v>
+        <v>120016450</v>
       </c>
       <c r="B20" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2647,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505439</v>
+        <v>505490</v>
       </c>
       <c r="R20" t="n">
-        <v>7133195</v>
+        <v>7133227</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2709,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016449</v>
+        <v>120016462</v>
       </c>
       <c r="B21" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,25 +2720,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505475</v>
+        <v>505473</v>
       </c>
       <c r="R21" t="n">
-        <v>7133313</v>
+        <v>7133190</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2811,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119999926</v>
+        <v>120016455</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,37 +2826,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505346</v>
+        <v>505301</v>
       </c>
       <c r="R22" t="n">
-        <v>7133517</v>
+        <v>7133536</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2913,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016462</v>
+        <v>119999926</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,41 +2924,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505473</v>
+        <v>505346</v>
       </c>
       <c r="R23" t="n">
-        <v>7133190</v>
+        <v>7133517</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3015,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016645</v>
+        <v>120016449</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>89650</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3031,37 +3030,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505457</v>
+        <v>505475</v>
       </c>
       <c r="R24" t="n">
-        <v>7133307</v>
+        <v>7133313</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3102,7 +3098,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3121,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016450</v>
+        <v>119987715</v>
       </c>
       <c r="B25" t="n">
-        <v>89650</v>
+        <v>92048</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,37 +3132,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505490</v>
+        <v>505497</v>
       </c>
       <c r="R25" t="n">
-        <v>7133227</v>
+        <v>7133163</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3223,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119985349</v>
+        <v>120016451</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,37 +3234,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505524</v>
+        <v>505439</v>
       </c>
       <c r="R26" t="n">
-        <v>7133131</v>
+        <v>7133195</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3299,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120016456</v>
+        <v>120016451</v>
       </c>
       <c r="B8" t="n">
-        <v>78278</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505473</v>
+        <v>505439</v>
       </c>
       <c r="R8" t="n">
-        <v>7133215</v>
+        <v>7133195</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,6 +1440,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120016645</v>
+        <v>120016462</v>
       </c>
       <c r="B9" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,41 +1483,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505457</v>
+        <v>505473</v>
       </c>
       <c r="R9" t="n">
-        <v>7133307</v>
+        <v>7133190</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1555,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1674,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016619</v>
+        <v>120016450</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>89650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,37 +1691,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505447</v>
+        <v>505490</v>
       </c>
       <c r="R11" t="n">
-        <v>7133184</v>
+        <v>7133227</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1761,7 +1759,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1780,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120016454</v>
+        <v>120016461</v>
       </c>
       <c r="B12" t="n">
-        <v>90857</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,25 +1789,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6008693</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505318</v>
+        <v>505294</v>
       </c>
       <c r="R12" t="n">
-        <v>7133504</v>
+        <v>7133539</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1856,11 +1853,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,10 +1879,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120016460</v>
+        <v>120016453</v>
       </c>
       <c r="B13" t="n">
-        <v>78187</v>
+        <v>92048</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,21 +1895,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505439</v>
+        <v>505463</v>
       </c>
       <c r="R13" t="n">
-        <v>7133195</v>
+        <v>7133176</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1989,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120016461</v>
+        <v>119987715</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,41 +1993,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505294</v>
+        <v>505497</v>
       </c>
       <c r="R14" t="n">
-        <v>7133539</v>
+        <v>7133163</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120016458</v>
+        <v>120016455</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,21 +2099,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505303</v>
+        <v>505301</v>
       </c>
       <c r="R15" t="n">
-        <v>7133532</v>
+        <v>7133536</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2193,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119996930</v>
+        <v>119985349</v>
       </c>
       <c r="B16" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2201,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,13 +2225,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505471</v>
+        <v>505524</v>
       </c>
       <c r="R16" t="n">
-        <v>7133319</v>
+        <v>7133131</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119987738</v>
+        <v>120016449</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>89650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,39 +2303,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505487</v>
+        <v>505475</v>
       </c>
       <c r="R17" t="n">
-        <v>7133194</v>
+        <v>7133313</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2402,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119985349</v>
+        <v>120016456</v>
       </c>
       <c r="B18" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,37 +2405,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505524</v>
+        <v>505473</v>
       </c>
       <c r="R18" t="n">
-        <v>7133131</v>
+        <v>7133215</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2504,10 +2491,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120016453</v>
+        <v>119987738</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,34 +2507,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505463</v>
+        <v>505487</v>
       </c>
       <c r="R19" t="n">
-        <v>7133176</v>
+        <v>7133194</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2606,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016450</v>
+        <v>120016619</v>
       </c>
       <c r="B20" t="n">
-        <v>89650</v>
+        <v>92048</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,34 +2614,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505490</v>
+        <v>505447</v>
       </c>
       <c r="R20" t="n">
-        <v>7133227</v>
+        <v>7133184</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2690,6 +2685,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2708,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016462</v>
+        <v>120016454</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>90857</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2720,25 +2716,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6008693</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505473</v>
+        <v>505318</v>
       </c>
       <c r="R21" t="n">
-        <v>7133190</v>
+        <v>7133504</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2784,6 +2780,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016455</v>
+        <v>119996930</v>
       </c>
       <c r="B22" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,37 +2827,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505301</v>
+        <v>505471</v>
       </c>
       <c r="R22" t="n">
-        <v>7133536</v>
+        <v>7133319</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2912,7 +2913,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119999926</v>
+        <v>120016458</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2948,17 +2949,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505346</v>
+        <v>505303</v>
       </c>
       <c r="R23" t="n">
-        <v>7133517</v>
+        <v>7133532</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3014,10 +3015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016449</v>
+        <v>119999926</v>
       </c>
       <c r="B24" t="n">
-        <v>89650</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,37 +3031,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505475</v>
+        <v>505346</v>
       </c>
       <c r="R24" t="n">
-        <v>7133313</v>
+        <v>7133517</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3116,10 +3117,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119987715</v>
+        <v>120016460</v>
       </c>
       <c r="B25" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,37 +3133,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505497</v>
+        <v>505439</v>
       </c>
       <c r="R25" t="n">
-        <v>7133163</v>
+        <v>7133195</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3218,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120016451</v>
+        <v>120016645</v>
       </c>
       <c r="B26" t="n">
-        <v>57473</v>
+        <v>79131</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,34 +3235,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505439</v>
+        <v>505457</v>
       </c>
       <c r="R26" t="n">
-        <v>7133195</v>
+        <v>7133307</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3296,17 +3300,13 @@
           <t>2024-09-25</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120016459</v>
+        <v>120016450</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>89650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505434</v>
+        <v>505490</v>
       </c>
       <c r="R10" t="n">
-        <v>7133465</v>
+        <v>7133227</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016450</v>
+        <v>120016459</v>
       </c>
       <c r="B11" t="n">
-        <v>89650</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,21 +1691,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505490</v>
+        <v>505434</v>
       </c>
       <c r="R11" t="n">
-        <v>7133227</v>
+        <v>7133465</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120016451</v>
+        <v>120016462</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,25 +1376,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505439</v>
+        <v>505473</v>
       </c>
       <c r="R8" t="n">
-        <v>7133195</v>
+        <v>7133190</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,11 +1440,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120016462</v>
+        <v>120016459</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505473</v>
+        <v>505434</v>
       </c>
       <c r="R9" t="n">
-        <v>7133190</v>
+        <v>7133465</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120016450</v>
+        <v>120016645</v>
       </c>
       <c r="B10" t="n">
-        <v>89650</v>
+        <v>79131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,34 +1584,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505490</v>
+        <v>505457</v>
       </c>
       <c r="R10" t="n">
-        <v>7133227</v>
+        <v>7133307</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1657,6 +1655,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016459</v>
+        <v>120016456</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505434</v>
+        <v>505473</v>
       </c>
       <c r="R11" t="n">
-        <v>7133465</v>
+        <v>7133215</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120016461</v>
+        <v>120016454</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>90857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,25 +1788,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6008693</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1817,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505294</v>
+        <v>505318</v>
       </c>
       <c r="R12" t="n">
-        <v>7133539</v>
+        <v>7133504</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1853,6 +1852,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120016453</v>
+        <v>119987738</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,34 +1899,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505463</v>
+        <v>505487</v>
       </c>
       <c r="R13" t="n">
-        <v>7133176</v>
+        <v>7133194</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1981,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119987715</v>
+        <v>120016450</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>89650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,37 +2006,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505497</v>
+        <v>505490</v>
       </c>
       <c r="R14" t="n">
-        <v>7133163</v>
+        <v>7133227</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120016455</v>
+        <v>120016453</v>
       </c>
       <c r="B15" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,21 +2108,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2123,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505301</v>
+        <v>505463</v>
       </c>
       <c r="R15" t="n">
-        <v>7133536</v>
+        <v>7133176</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2185,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119985349</v>
+        <v>120016458</v>
       </c>
       <c r="B16" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,37 +2210,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505524</v>
+        <v>505303</v>
       </c>
       <c r="R16" t="n">
-        <v>7133131</v>
+        <v>7133532</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2287,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120016449</v>
+        <v>120016460</v>
       </c>
       <c r="B17" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,21 +2312,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2327,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505475</v>
+        <v>505439</v>
       </c>
       <c r="R17" t="n">
-        <v>7133313</v>
+        <v>7133195</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2389,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016456</v>
+        <v>120016619</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,34 +2414,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505473</v>
+        <v>505447</v>
       </c>
       <c r="R18" t="n">
-        <v>7133215</v>
+        <v>7133184</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2473,6 +2485,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2491,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119987738</v>
+        <v>119999926</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,42 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505487</v>
+        <v>505346</v>
       </c>
       <c r="R19" t="n">
-        <v>7133194</v>
+        <v>7133517</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016619</v>
+        <v>120016455</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2614,37 +2622,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505447</v>
+        <v>505301</v>
       </c>
       <c r="R20" t="n">
-        <v>7133184</v>
+        <v>7133536</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2685,7 +2690,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2704,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016454</v>
+        <v>120016449</v>
       </c>
       <c r="B21" t="n">
-        <v>90857</v>
+        <v>89650</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,25 +2720,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6008693</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2744,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505318</v>
+        <v>505475</v>
       </c>
       <c r="R21" t="n">
-        <v>7133504</v>
+        <v>7133313</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2780,11 +2784,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016458</v>
+        <v>119987715</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2929,37 +2928,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505303</v>
+        <v>505497</v>
       </c>
       <c r="R23" t="n">
-        <v>7133532</v>
+        <v>7133163</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3015,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119999926</v>
+        <v>119985349</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3031,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3055,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505346</v>
+        <v>505524</v>
       </c>
       <c r="R24" t="n">
-        <v>7133517</v>
+        <v>7133131</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3117,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016460</v>
+        <v>120016461</v>
       </c>
       <c r="B25" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,25 +3128,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3157,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505439</v>
+        <v>505294</v>
       </c>
       <c r="R25" t="n">
-        <v>7133195</v>
+        <v>7133539</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3219,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120016645</v>
+        <v>120016451</v>
       </c>
       <c r="B26" t="n">
-        <v>79131</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,37 +3234,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505457</v>
+        <v>505439</v>
       </c>
       <c r="R26" t="n">
-        <v>7133307</v>
+        <v>7133195</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3300,13 +3296,17 @@
           <t>2024-09-25</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120016462</v>
+        <v>120016453</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,25 +1376,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505473</v>
+        <v>505463</v>
       </c>
       <c r="R8" t="n">
-        <v>7133190</v>
+        <v>7133176</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120016459</v>
+        <v>120016458</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505434</v>
+        <v>505303</v>
       </c>
       <c r="R9" t="n">
-        <v>7133465</v>
+        <v>7133532</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120016645</v>
+        <v>119987738</v>
       </c>
       <c r="B10" t="n">
-        <v>79131</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,37 +1584,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505457</v>
+        <v>505487</v>
       </c>
       <c r="R10" t="n">
-        <v>7133307</v>
+        <v>7133194</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1657,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1674,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016456</v>
+        <v>120016462</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1687,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,7 +1718,7 @@
         <v>505473</v>
       </c>
       <c r="R11" t="n">
-        <v>7133215</v>
+        <v>7133190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1883,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119987738</v>
+        <v>119987715</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>92048</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,42 +1900,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505487</v>
+        <v>505497</v>
       </c>
       <c r="R13" t="n">
-        <v>7133194</v>
+        <v>7133163</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,7 +1986,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120016450</v>
+        <v>120016449</v>
       </c>
       <c r="B14" t="n">
         <v>89650</v>
@@ -2030,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505490</v>
+        <v>505475</v>
       </c>
       <c r="R14" t="n">
-        <v>7133227</v>
+        <v>7133313</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2092,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120016453</v>
+        <v>119985349</v>
       </c>
       <c r="B15" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,37 +2104,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505463</v>
+        <v>505524</v>
       </c>
       <c r="R15" t="n">
-        <v>7133176</v>
+        <v>7133131</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,10 +2190,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120016458</v>
+        <v>120016455</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2234,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505303</v>
+        <v>505301</v>
       </c>
       <c r="R16" t="n">
-        <v>7133532</v>
+        <v>7133536</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2296,10 +2292,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120016460</v>
+        <v>119996930</v>
       </c>
       <c r="B17" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,37 +2308,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505439</v>
+        <v>505471</v>
       </c>
       <c r="R17" t="n">
-        <v>7133195</v>
+        <v>7133319</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016619</v>
+        <v>120016450</v>
       </c>
       <c r="B18" t="n">
-        <v>92048</v>
+        <v>89650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,37 +2410,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505447</v>
+        <v>505490</v>
       </c>
       <c r="R18" t="n">
-        <v>7133184</v>
+        <v>7133227</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2485,7 +2478,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2504,7 +2496,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119999926</v>
+        <v>120016459</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2540,17 +2532,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505346</v>
+        <v>505434</v>
       </c>
       <c r="R19" t="n">
-        <v>7133517</v>
+        <v>7133465</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2606,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016455</v>
+        <v>120016645</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,34 +2614,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505301</v>
+        <v>505457</v>
       </c>
       <c r="R20" t="n">
-        <v>7133536</v>
+        <v>7133307</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2690,6 +2685,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2708,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120016449</v>
+        <v>120016460</v>
       </c>
       <c r="B21" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,21 +2720,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505475</v>
+        <v>505439</v>
       </c>
       <c r="R21" t="n">
-        <v>7133313</v>
+        <v>7133195</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2810,10 +2806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119996930</v>
+        <v>119999926</v>
       </c>
       <c r="B22" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2822,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,13 +2846,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505471</v>
+        <v>505346</v>
       </c>
       <c r="R22" t="n">
-        <v>7133319</v>
+        <v>7133517</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2912,10 +2908,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119987715</v>
+        <v>120016451</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,37 +2924,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505497</v>
+        <v>505439</v>
       </c>
       <c r="R23" t="n">
-        <v>7133163</v>
+        <v>7133195</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2988,6 +2984,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119985349</v>
+        <v>120016619</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>92048</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,37 +3031,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505524</v>
+        <v>505447</v>
       </c>
       <c r="R24" t="n">
-        <v>7133131</v>
+        <v>7133184</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,6 +3102,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3116,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120016461</v>
+        <v>120016456</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3128,25 +3133,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505294</v>
+        <v>505473</v>
       </c>
       <c r="R25" t="n">
-        <v>7133539</v>
+        <v>7133215</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3218,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120016451</v>
+        <v>120016461</v>
       </c>
       <c r="B26" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3230,25 +3235,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>505439</v>
+        <v>505294</v>
       </c>
       <c r="R26" t="n">
-        <v>7133195</v>
+        <v>7133539</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3294,11 +3299,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -2292,10 +2292,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119996930</v>
+        <v>120016450</v>
       </c>
       <c r="B17" t="n">
-        <v>78279</v>
+        <v>89650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2308,37 +2308,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505471</v>
+        <v>505490</v>
       </c>
       <c r="R17" t="n">
-        <v>7133319</v>
+        <v>7133227</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016450</v>
+        <v>119996930</v>
       </c>
       <c r="B18" t="n">
-        <v>89650</v>
+        <v>78279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2410,37 +2410,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505490</v>
+        <v>505471</v>
       </c>
       <c r="R18" t="n">
-        <v>7133227</v>
+        <v>7133319</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 30406-2020 artfynd.xlsx
+++ b/artfynd/A 30406-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88774724</v>
+        <v>89602968</v>
       </c>
       <c r="B2" t="n">
-        <v>91139</v>
+        <v>89945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,22 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505333</v>
+        <v>505333.1892962086</v>
       </c>
       <c r="R2" t="n">
-        <v>7133475</v>
+        <v>7133474.905035073</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,14 +748,19 @@
           <t>2020-10-28</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På stående död asp</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -779,14 +780,18 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88782328</v>
+        <v>89602999</v>
       </c>
       <c r="B3" t="n">
         <v>78503</v>
@@ -820,22 +825,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505449.7780318622</v>
+        <v>505450.2130584756</v>
       </c>
       <c r="R3" t="n">
-        <v>7133355.407912654</v>
+        <v>7133354.974973971</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,17 +896,21 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89602999</v>
+        <v>108432746</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
+        <v>78472</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505450.2130584756</v>
+        <v>505412.3753677196</v>
       </c>
       <c r="R4" t="n">
-        <v>7133354.974973971</v>
+        <v>7133387.436194601</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +977,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2011-08-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -982,7 +987,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2011-08-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -990,38 +995,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rik förekomst på asp</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89602968</v>
+        <v>108432743</v>
       </c>
       <c r="B5" t="n">
-        <v>89945</v>
+        <v>90645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1037,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2046</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vit aspticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Favolus pseudobetulinus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505333.1892962086</v>
+        <v>505329.1081459846</v>
       </c>
       <c r="R5" t="n">
-        <v>7133474.905035073</v>
+        <v>7133574.645788469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1095,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2011-08-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1098,7 +1105,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2011-08-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1118,26 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108432746</v>
+        <v>120016449</v>
       </c>
       <c r="B6" t="n">
-        <v>78472</v>
+        <v>89650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>388</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505412.3753677196</v>
+        <v>505475</v>
       </c>
       <c r="R6" t="n">
-        <v>7133387.436194601</v>
+        <v>7133313</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,27 +1207,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rik förekomst på asp</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,29 +1221,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108432743</v>
+        <v>120016454</v>
       </c>
       <c r="B7" t="n">
-        <v>90645</v>
+        <v>90857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>6008693</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Resinoporia crassa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Audet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505329.1081459846</v>
+        <v>505318</v>
       </c>
       <c r="R7" t="n">
-        <v>7133574.645788469</v>
+        <v>7133504</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,22 +1309,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,22 +1334,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120016449</v>
+        <v>119999926</v>
       </c>
       <c r="B8" t="n">
-        <v>89650</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,37 +1362,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505475</v>
+        <v>505346</v>
       </c>
       <c r="R8" t="n">
-        <v>7133313</v>
+        <v>7133517</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120016454</v>
+        <v>120016459</v>
       </c>
       <c r="B9" t="n">
-        <v>90857</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1460,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6008693</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Resinoporia crassa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Audet</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505318</v>
+        <v>505434</v>
       </c>
       <c r="R9" t="n">
-        <v>7133504</v>
+        <v>7133465</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1542,11 +1524,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119999926</v>
+        <v>120016461</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,41 +1562,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505346</v>
+        <v>505294</v>
       </c>
       <c r="R10" t="n">
-        <v>7133517</v>
+        <v>7133539</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120016459</v>
+        <v>119985349</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,37 +1668,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505434</v>
+        <v>505524</v>
       </c>
       <c r="R11" t="n">
-        <v>7133465</v>
+        <v>7133131</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120016461</v>
+        <v>120016458</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,25 +1766,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1817,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505294</v>
+        <v>505303</v>
       </c>
       <c r="R12" t="n">
-        <v>7133539</v>
+        <v>7133532</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119985349</v>
+        <v>120016645</v>
       </c>
       <c r="B13" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,37 +1872,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505524</v>
+        <v>505457</v>
       </c>
       <c r="R13" t="n">
-        <v>7133131</v>
+        <v>7133307</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,6 +1943,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1981,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120016458</v>
+        <v>120016451</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2021,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505303</v>
+        <v>505439</v>
       </c>
       <c r="R14" t="n">
-        <v>7133532</v>
+        <v>7133195</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2057,6 +2038,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2083,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120016645</v>
+        <v>120016450</v>
       </c>
       <c r="B15" t="n">
-        <v>79131</v>
+        <v>89650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,37 +2085,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505457</v>
+        <v>505490</v>
       </c>
       <c r="R15" t="n">
-        <v>7133307</v>
+        <v>7133227</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2170,7 +2153,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2189,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120016451</v>
+        <v>120016456</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>78278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,21 +2187,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2229,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505439</v>
+        <v>505473</v>
       </c>
       <c r="R16" t="n">
-        <v>7133195</v>
+        <v>7133215</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2265,11 +2247,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120016450</v>
+        <v>120016455</v>
       </c>
       <c r="B17" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,21 +2289,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2336,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505490</v>
+        <v>505301</v>
       </c>
       <c r="R17" t="n">
-        <v>7133227</v>
+        <v>7133536</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2398,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120016456</v>
+        <v>120016619</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,34 +2391,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505473</v>
+        <v>505447</v>
       </c>
       <c r="R18" t="n">
-        <v>7133215</v>
+        <v>7133184</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2482,6 +2462,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2500,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120016455</v>
+        <v>119987715</v>
       </c>
       <c r="B19" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,37 +2497,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505301</v>
+        <v>505497</v>
       </c>
       <c r="R19" t="n">
-        <v>7133536</v>
+        <v>7133163</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,7 +2583,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120016619</v>
+        <v>120016453</v>
       </c>
       <c r="B20" t="n">
         <v>92048</v>
@@ -2636,19 +2617,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505447</v>
+        <v>505463</v>
       </c>
       <c r="R20" t="n">
-        <v>7133184</v>
+        <v>7133176</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2689,7 +2667,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2708,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119987715</v>
+        <v>120016460</v>
       </c>
       <c r="B21" t="n">
-        <v>92048</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,37 +2701,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>505497</v>
+        <v>505439</v>
       </c>
       <c r="R21" t="n">
-        <v>7133163</v>
+        <v>7133195</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2810,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120016453</v>
+        <v>120016462</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,25 +2799,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505463</v>
+        <v>505473</v>
       </c>
       <c r="R22" t="n">
-        <v>7133176</v>
+        <v>7133190</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2912,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120016460</v>
+        <v>119987738</v>
       </c>
       <c r="B23" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,34 +2905,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>505439</v>
+        <v>505487</v>
       </c>
       <c r="R23" t="n">
-        <v>7133195</v>
+        <v>7133194</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3014,10 +2996,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120016462</v>
+        <v>119996930</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3026,41 +3008,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505473</v>
+        <v>505471</v>
       </c>
       <c r="R24" t="n">
-        <v>7133190</v>
+        <v>7133319</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3116,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119987738</v>
+        <v>120016452</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>91904</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3128,43 +3110,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>232140</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>505487</v>
+        <v>505321</v>
       </c>
       <c r="R25" t="n">
-        <v>7133194</v>
+        <v>7133503</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3199,12 +3179,18 @@
           <t>2024-09-25</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Under tallåga</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3220,219 +3206,6 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>119996930</v>
-      </c>
-      <c r="B26" t="n">
-        <v>78279</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>505471</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7133319</v>
-      </c>
-      <c r="S26" t="n">
-        <v>20</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>120016452</v>
-      </c>
-      <c r="B27" t="n">
-        <v>91904</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>232140</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tajgataggsvamp</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Phellodon secretus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>505321</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7133503</v>
-      </c>
-      <c r="S27" t="n">
-        <v>25</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Under tallåga</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
